--- a/reports/Debug-purgatory-20260111/Month to Date (Actual)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260111/Month to Date (Actual)_Visits.xlsx
@@ -34,16 +34,16 @@
     <t>Purgatory Passes</t>
   </si>
   <si>
-    <t>Purgatory Comp Tickets</t>
+    <t>Purgatory Coaster</t>
+  </si>
+  <si>
+    <t>Purgatory Tickets</t>
   </si>
   <si>
     <t>Purgatory Uplift Tickets</t>
   </si>
   <si>
-    <t>Purgatory Tickets</t>
-  </si>
-  <si>
-    <t>Purgatory Coaster</t>
+    <t>Purgatory Comp Tickets</t>
   </si>
 </sst>
 </file>
@@ -437,7 +437,7 @@
         <v>46023</v>
       </c>
       <c r="C2" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,13 +448,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C3" s="2">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -462,13 +462,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C4" s="2">
-        <v>12</v>
+        <v>1455</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -476,10 +476,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="2">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="C5" s="2">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>5</v>
@@ -490,10 +490,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="2">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="C6" s="2">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>5</v>
@@ -504,10 +504,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="2">
-        <v>46028</v>
+        <v>46025</v>
       </c>
       <c r="C7" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
@@ -518,10 +518,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>46030</v>
+        <v>46026</v>
       </c>
       <c r="C8" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
@@ -532,10 +532,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>46030</v>
+        <v>46026</v>
       </c>
       <c r="C9" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>5</v>
@@ -546,10 +546,10 @@
         <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>46031</v>
+        <v>46027</v>
       </c>
       <c r="C10" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>5</v>
@@ -560,13 +560,13 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>46031</v>
+        <v>46027</v>
       </c>
       <c r="C11" s="2">
-        <v>145</v>
+        <v>1403</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -574,10 +574,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="2">
-        <v>46032</v>
+        <v>46027</v>
       </c>
       <c r="C12" s="2">
-        <v>105</v>
+        <v>48</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>5</v>
@@ -588,10 +588,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>46033</v>
+        <v>46028</v>
       </c>
       <c r="C13" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>5</v>
@@ -602,10 +602,10 @@
         <v>1</v>
       </c>
       <c r="B14" s="2">
-        <v>46033</v>
+        <v>46028</v>
       </c>
       <c r="C14" s="2">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>5</v>
@@ -616,10 +616,10 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>46033</v>
+        <v>46029</v>
       </c>
       <c r="C15" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>5</v>
@@ -630,10 +630,10 @@
         <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>46033</v>
+        <v>46030</v>
       </c>
       <c r="C16" s="2">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>5</v>
@@ -644,10 +644,10 @@
         <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>46023</v>
+        <v>46031</v>
       </c>
       <c r="C17" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>5</v>
@@ -658,13 +658,13 @@
         <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>46024</v>
+        <v>46031</v>
       </c>
       <c r="C18" s="2">
-        <v>608</v>
+        <v>1</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -672,13 +672,13 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>46024</v>
+        <v>46032</v>
       </c>
       <c r="C19" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -686,10 +686,10 @@
         <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>46025</v>
+        <v>46032</v>
       </c>
       <c r="C20" s="2">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>5</v>
@@ -700,10 +700,10 @@
         <v>1</v>
       </c>
       <c r="B21" s="2">
-        <v>46025</v>
+        <v>46033</v>
       </c>
       <c r="C21" s="2">
-        <v>1469</v>
+        <v>1375</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>5</v>
@@ -714,10 +714,10 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>46025</v>
+        <v>46033</v>
       </c>
       <c r="C22" s="2">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>5</v>
@@ -728,13 +728,13 @@
         <v>1</v>
       </c>
       <c r="B23" s="2">
-        <v>46026</v>
+        <v>46023</v>
       </c>
       <c r="C23" s="2">
-        <v>906</v>
+        <v>1</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -742,13 +742,13 @@
         <v>1</v>
       </c>
       <c r="B24" s="2">
-        <v>46026</v>
+        <v>46023</v>
       </c>
       <c r="C24" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -756,10 +756,10 @@
         <v>1</v>
       </c>
       <c r="B25" s="2">
-        <v>46026</v>
+        <v>46023</v>
       </c>
       <c r="C25" s="2">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>5</v>
@@ -770,13 +770,13 @@
         <v>1</v>
       </c>
       <c r="B26" s="2">
-        <v>46027</v>
+        <v>46024</v>
       </c>
       <c r="C26" s="2">
-        <v>17</v>
+        <v>1445</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -784,10 +784,10 @@
         <v>1</v>
       </c>
       <c r="B27" s="2">
-        <v>46028</v>
+        <v>46025</v>
       </c>
       <c r="C27" s="2">
-        <v>568</v>
+        <v>1</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>5</v>
@@ -798,10 +798,10 @@
         <v>1</v>
       </c>
       <c r="B28" s="2">
-        <v>46028</v>
+        <v>46026</v>
       </c>
       <c r="C28" s="2">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>5</v>
@@ -812,13 +812,13 @@
         <v>1</v>
       </c>
       <c r="B29" s="2">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="C29" s="2">
-        <v>1128</v>
+        <v>565</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -826,13 +826,13 @@
         <v>1</v>
       </c>
       <c r="B30" s="2">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="C30" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -840,10 +840,10 @@
         <v>1</v>
       </c>
       <c r="B31" s="2">
-        <v>46031</v>
+        <v>46029</v>
       </c>
       <c r="C31" s="2">
-        <v>1354</v>
+        <v>38</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>5</v>
@@ -854,13 +854,13 @@
         <v>1</v>
       </c>
       <c r="B32" s="2">
-        <v>46032</v>
+        <v>46030</v>
       </c>
       <c r="C32" s="2">
-        <v>849</v>
+        <v>667</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -868,13 +868,13 @@
         <v>1</v>
       </c>
       <c r="B33" s="2">
-        <v>46033</v>
+        <v>46030</v>
       </c>
       <c r="C33" s="2">
-        <v>14</v>
+        <v>976</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -882,10 +882,10 @@
         <v>1</v>
       </c>
       <c r="B34" s="2">
-        <v>46023</v>
+        <v>46032</v>
       </c>
       <c r="C34" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>5</v>
@@ -896,13 +896,13 @@
         <v>1</v>
       </c>
       <c r="B35" s="2">
-        <v>46023</v>
+        <v>46032</v>
       </c>
       <c r="C35" s="2">
-        <v>1552</v>
+        <v>22</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -910,10 +910,10 @@
         <v>1</v>
       </c>
       <c r="B36" s="2">
-        <v>46023</v>
+        <v>46032</v>
       </c>
       <c r="C36" s="2">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>5</v>
@@ -924,10 +924,10 @@
         <v>1</v>
       </c>
       <c r="B37" s="2">
-        <v>46023</v>
+        <v>46033</v>
       </c>
       <c r="C37" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>5</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="B38" s="2">
-        <v>46026</v>
+        <v>46033</v>
       </c>
       <c r="C38" s="2">
-        <v>22</v>
+        <v>533</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -952,10 +952,10 @@
         <v>1</v>
       </c>
       <c r="B39" s="2">
-        <v>46026</v>
+        <v>46033</v>
       </c>
       <c r="C39" s="2">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>5</v>
@@ -966,13 +966,13 @@
         <v>1</v>
       </c>
       <c r="B40" s="2">
-        <v>46027</v>
+        <v>46023</v>
       </c>
       <c r="C40" s="2">
-        <v>13</v>
+        <v>528</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -980,13 +980,13 @@
         <v>1</v>
       </c>
       <c r="B41" s="2">
-        <v>46027</v>
+        <v>46023</v>
       </c>
       <c r="C41" s="2">
-        <v>322</v>
+        <v>936</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -994,10 +994,10 @@
         <v>1</v>
       </c>
       <c r="B42" s="2">
-        <v>46028</v>
+        <v>46024</v>
       </c>
       <c r="C42" s="2">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>5</v>
@@ -1008,7 +1008,7 @@
         <v>1</v>
       </c>
       <c r="B43" s="2">
-        <v>46029</v>
+        <v>46024</v>
       </c>
       <c r="C43" s="2">
         <v>1</v>
@@ -1022,10 +1022,10 @@
         <v>1</v>
       </c>
       <c r="B44" s="2">
-        <v>46029</v>
+        <v>46025</v>
       </c>
       <c r="C44" s="2">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>5</v>
@@ -1036,13 +1036,13 @@
         <v>1</v>
       </c>
       <c r="B45" s="2">
-        <v>46029</v>
+        <v>46026</v>
       </c>
       <c r="C45" s="2">
-        <v>2</v>
+        <v>311</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1050,10 +1050,10 @@
         <v>1</v>
       </c>
       <c r="B46" s="2">
-        <v>46030</v>
+        <v>46026</v>
       </c>
       <c r="C46" s="2">
-        <v>7</v>
+        <v>969</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>5</v>
@@ -1064,13 +1064,13 @@
         <v>1</v>
       </c>
       <c r="B47" s="2">
-        <v>46030</v>
+        <v>46027</v>
       </c>
       <c r="C47" s="2">
-        <v>138</v>
+        <v>68</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1078,10 +1078,10 @@
         <v>1</v>
       </c>
       <c r="B48" s="2">
-        <v>46031</v>
+        <v>46028</v>
       </c>
       <c r="C48" s="2">
-        <v>139</v>
+        <v>4</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>5</v>
@@ -1092,10 +1092,10 @@
         <v>1</v>
       </c>
       <c r="B49" s="2">
-        <v>46033</v>
+        <v>46029</v>
       </c>
       <c r="C49" s="2">
-        <v>30</v>
+        <v>183</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>9</v>
@@ -1106,13 +1106,13 @@
         <v>1</v>
       </c>
       <c r="B50" s="2">
-        <v>46033</v>
+        <v>46029</v>
       </c>
       <c r="C50" s="2">
-        <v>84</v>
+        <v>3</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1120,10 +1120,10 @@
         <v>1</v>
       </c>
       <c r="B51" s="2">
-        <v>46023</v>
+        <v>46030</v>
       </c>
       <c r="C51" s="2">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>5</v>
@@ -1134,10 +1134,10 @@
         <v>1</v>
       </c>
       <c r="B52" s="2">
-        <v>46024</v>
+        <v>46032</v>
       </c>
       <c r="C52" s="2">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>5</v>
@@ -1148,13 +1148,13 @@
         <v>1</v>
       </c>
       <c r="B53" s="2">
-        <v>46024</v>
+        <v>46032</v>
       </c>
       <c r="C53" s="2">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1162,13 +1162,13 @@
         <v>1</v>
       </c>
       <c r="B54" s="2">
-        <v>46024</v>
+        <v>46032</v>
       </c>
       <c r="C54" s="2">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1176,10 +1176,10 @@
         <v>1</v>
       </c>
       <c r="B55" s="2">
-        <v>46024</v>
+        <v>46033</v>
       </c>
       <c r="C55" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>5</v>
@@ -1190,13 +1190,13 @@
         <v>1</v>
       </c>
       <c r="B56" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C56" s="2">
-        <v>406</v>
+        <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1204,10 +1204,10 @@
         <v>1</v>
       </c>
       <c r="B57" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C57" s="2">
-        <v>2</v>
+        <v>1552</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>7</v>
@@ -1218,10 +1218,10 @@
         <v>1</v>
       </c>
       <c r="B58" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C58" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>5</v>
@@ -1232,10 +1232,10 @@
         <v>1</v>
       </c>
       <c r="B59" s="2">
-        <v>46026</v>
+        <v>46023</v>
       </c>
       <c r="C59" s="2">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>5</v>
@@ -1246,10 +1246,10 @@
         <v>1</v>
       </c>
       <c r="B60" s="2">
-        <v>46028</v>
+        <v>46026</v>
       </c>
       <c r="C60" s="2">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>5</v>
@@ -1260,13 +1260,13 @@
         <v>1</v>
       </c>
       <c r="B61" s="2">
-        <v>46028</v>
+        <v>46026</v>
       </c>
       <c r="C61" s="2">
-        <v>258</v>
+        <v>19</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1274,10 +1274,10 @@
         <v>1</v>
       </c>
       <c r="B62" s="2">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="C62" s="2">
-        <v>84</v>
+        <v>13</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>5</v>
@@ -1288,13 +1288,13 @@
         <v>1</v>
       </c>
       <c r="B63" s="2">
-        <v>46031</v>
+        <v>46027</v>
       </c>
       <c r="C63" s="2">
-        <v>7</v>
+        <v>322</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1302,13 +1302,13 @@
         <v>1</v>
       </c>
       <c r="B64" s="2">
-        <v>46031</v>
+        <v>46028</v>
       </c>
       <c r="C64" s="2">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1316,13 +1316,13 @@
         <v>1</v>
       </c>
       <c r="B65" s="2">
-        <v>46032</v>
+        <v>46029</v>
       </c>
       <c r="C65" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1330,10 +1330,10 @@
         <v>1</v>
       </c>
       <c r="B66" s="2">
-        <v>46023</v>
+        <v>46029</v>
       </c>
       <c r="C66" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>5</v>
@@ -1344,13 +1344,13 @@
         <v>1</v>
       </c>
       <c r="B67" s="2">
-        <v>46023</v>
+        <v>46029</v>
       </c>
       <c r="C67" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1358,13 +1358,13 @@
         <v>1</v>
       </c>
       <c r="B68" s="2">
-        <v>46024</v>
+        <v>46030</v>
       </c>
       <c r="C68" s="2">
-        <v>1455</v>
+        <v>7</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1372,13 +1372,13 @@
         <v>1</v>
       </c>
       <c r="B69" s="2">
-        <v>46025</v>
+        <v>46030</v>
       </c>
       <c r="C69" s="2">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1386,10 +1386,10 @@
         <v>1</v>
       </c>
       <c r="B70" s="2">
-        <v>46025</v>
+        <v>46031</v>
       </c>
       <c r="C70" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>5</v>
@@ -1400,13 +1400,13 @@
         <v>1</v>
       </c>
       <c r="B71" s="2">
-        <v>46025</v>
+        <v>46033</v>
       </c>
       <c r="C71" s="2">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1414,13 +1414,13 @@
         <v>1</v>
       </c>
       <c r="B72" s="2">
-        <v>46026</v>
+        <v>46033</v>
       </c>
       <c r="C72" s="2">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1428,10 +1428,10 @@
         <v>1</v>
       </c>
       <c r="B73" s="2">
-        <v>46026</v>
+        <v>46023</v>
       </c>
       <c r="C73" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>5</v>
@@ -1442,13 +1442,13 @@
         <v>1</v>
       </c>
       <c r="B74" s="2">
-        <v>46027</v>
+        <v>46024</v>
       </c>
       <c r="C74" s="2">
-        <v>1</v>
+        <v>608</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1456,10 +1456,10 @@
         <v>1</v>
       </c>
       <c r="B75" s="2">
-        <v>46027</v>
+        <v>46024</v>
       </c>
       <c r="C75" s="2">
-        <v>1403</v>
+        <v>0</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>8</v>
@@ -1470,10 +1470,10 @@
         <v>1</v>
       </c>
       <c r="B76" s="2">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="C76" s="2">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>5</v>
@@ -1484,10 +1484,10 @@
         <v>1</v>
       </c>
       <c r="B77" s="2">
-        <v>46028</v>
+        <v>46025</v>
       </c>
       <c r="C77" s="2">
-        <v>6</v>
+        <v>1469</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>5</v>
@@ -1498,10 +1498,10 @@
         <v>1</v>
       </c>
       <c r="B78" s="2">
-        <v>46028</v>
+        <v>46025</v>
       </c>
       <c r="C78" s="2">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>5</v>
@@ -1512,13 +1512,13 @@
         <v>1</v>
       </c>
       <c r="B79" s="2">
-        <v>46029</v>
+        <v>46026</v>
       </c>
       <c r="C79" s="2">
-        <v>6</v>
+        <v>906</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -1526,10 +1526,10 @@
         <v>1</v>
       </c>
       <c r="B80" s="2">
-        <v>46030</v>
+        <v>46026</v>
       </c>
       <c r="C80" s="2">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>5</v>
@@ -1540,10 +1540,10 @@
         <v>1</v>
       </c>
       <c r="B81" s="2">
-        <v>46031</v>
+        <v>46026</v>
       </c>
       <c r="C81" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>5</v>
@@ -1554,13 +1554,13 @@
         <v>1</v>
       </c>
       <c r="B82" s="2">
-        <v>46031</v>
+        <v>46027</v>
       </c>
       <c r="C82" s="2">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1568,10 +1568,10 @@
         <v>1</v>
       </c>
       <c r="B83" s="2">
-        <v>46032</v>
+        <v>46028</v>
       </c>
       <c r="C83" s="2">
-        <v>4</v>
+        <v>568</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>5</v>
@@ -1582,10 +1582,10 @@
         <v>1</v>
       </c>
       <c r="B84" s="2">
-        <v>46032</v>
+        <v>46028</v>
       </c>
       <c r="C84" s="2">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>5</v>
@@ -1596,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="B85" s="2">
-        <v>46033</v>
+        <v>46029</v>
       </c>
       <c r="C85" s="2">
-        <v>1375</v>
+        <v>1128</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1610,13 +1610,13 @@
         <v>1</v>
       </c>
       <c r="B86" s="2">
-        <v>46033</v>
+        <v>46030</v>
       </c>
       <c r="C86" s="2">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1624,10 +1624,10 @@
         <v>1</v>
       </c>
       <c r="B87" s="2">
-        <v>46023</v>
+        <v>46031</v>
       </c>
       <c r="C87" s="2">
-        <v>1</v>
+        <v>1354</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>5</v>
@@ -1638,10 +1638,10 @@
         <v>1</v>
       </c>
       <c r="B88" s="2">
-        <v>46023</v>
+        <v>46032</v>
       </c>
       <c r="C88" s="2">
-        <v>12</v>
+        <v>849</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>7</v>
@@ -1652,10 +1652,10 @@
         <v>1</v>
       </c>
       <c r="B89" s="2">
-        <v>46023</v>
+        <v>46033</v>
       </c>
       <c r="C89" s="2">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>5</v>
@@ -1666,10 +1666,10 @@
         <v>1</v>
       </c>
       <c r="B90" s="2">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C90" s="2">
-        <v>1445</v>
+        <v>1</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>5</v>
@@ -1680,10 +1680,10 @@
         <v>1</v>
       </c>
       <c r="B91" s="2">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C91" s="2">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>5</v>
@@ -1694,10 +1694,10 @@
         <v>1</v>
       </c>
       <c r="B92" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C92" s="2">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>5</v>
@@ -1708,10 +1708,10 @@
         <v>1</v>
       </c>
       <c r="B93" s="2">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="C93" s="2">
-        <v>565</v>
+        <v>2</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>5</v>
@@ -1722,13 +1722,13 @@
         <v>1</v>
       </c>
       <c r="B94" s="2">
-        <v>46029</v>
+        <v>46025</v>
       </c>
       <c r="C94" s="2">
-        <v>2</v>
+        <v>310</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -1736,13 +1736,13 @@
         <v>1</v>
       </c>
       <c r="B95" s="2">
-        <v>46029</v>
+        <v>46025</v>
       </c>
       <c r="C95" s="2">
-        <v>38</v>
+        <v>1099</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -1750,10 +1750,10 @@
         <v>1</v>
       </c>
       <c r="B96" s="2">
-        <v>46030</v>
+        <v>46027</v>
       </c>
       <c r="C96" s="2">
-        <v>667</v>
+        <v>2</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>5</v>
@@ -1764,13 +1764,13 @@
         <v>1</v>
       </c>
       <c r="B97" s="2">
-        <v>46030</v>
+        <v>46027</v>
       </c>
       <c r="C97" s="2">
-        <v>976</v>
+        <v>3</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -1778,10 +1778,10 @@
         <v>1</v>
       </c>
       <c r="B98" s="2">
-        <v>46032</v>
+        <v>46028</v>
       </c>
       <c r="C98" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>5</v>
@@ -1792,13 +1792,13 @@
         <v>1</v>
       </c>
       <c r="B99" s="2">
-        <v>46032</v>
+        <v>46028</v>
       </c>
       <c r="C99" s="2">
-        <v>22</v>
+        <v>1411</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -1806,10 +1806,10 @@
         <v>1</v>
       </c>
       <c r="B100" s="2">
-        <v>46032</v>
+        <v>46029</v>
       </c>
       <c r="C100" s="2">
-        <v>44</v>
+        <v>460</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>5</v>
@@ -1820,10 +1820,10 @@
         <v>1</v>
       </c>
       <c r="B101" s="2">
-        <v>46033</v>
+        <v>46030</v>
       </c>
       <c r="C101" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>5</v>
@@ -1834,13 +1834,13 @@
         <v>1</v>
       </c>
       <c r="B102" s="2">
-        <v>46033</v>
+        <v>46031</v>
       </c>
       <c r="C102" s="2">
-        <v>533</v>
+        <v>5</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1848,10 +1848,10 @@
         <v>1</v>
       </c>
       <c r="B103" s="2">
-        <v>46033</v>
+        <v>46031</v>
       </c>
       <c r="C103" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>5</v>
@@ -1862,13 +1862,13 @@
         <v>1</v>
       </c>
       <c r="B104" s="2">
-        <v>46023</v>
+        <v>46031</v>
       </c>
       <c r="C104" s="2">
-        <v>1</v>
+        <v>836</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -1876,10 +1876,10 @@
         <v>1</v>
       </c>
       <c r="B105" s="2">
-        <v>46024</v>
+        <v>46031</v>
       </c>
       <c r="C105" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>5</v>
@@ -1890,10 +1890,10 @@
         <v>1</v>
       </c>
       <c r="B106" s="2">
-        <v>46024</v>
+        <v>46031</v>
       </c>
       <c r="C106" s="2">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>5</v>
@@ -1904,10 +1904,10 @@
         <v>1</v>
       </c>
       <c r="B107" s="2">
-        <v>46025</v>
+        <v>46032</v>
       </c>
       <c r="C107" s="2">
-        <v>2</v>
+        <v>2029</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>5</v>
@@ -1918,13 +1918,13 @@
         <v>1</v>
       </c>
       <c r="B108" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C108" s="2">
-        <v>310</v>
+        <v>4</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -1932,13 +1932,13 @@
         <v>1</v>
       </c>
       <c r="B109" s="2">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C109" s="2">
-        <v>1099</v>
+        <v>27</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -1946,10 +1946,10 @@
         <v>1</v>
       </c>
       <c r="B110" s="2">
-        <v>46027</v>
+        <v>46026</v>
       </c>
       <c r="C110" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>5</v>
@@ -1963,7 +1963,7 @@
         <v>46027</v>
       </c>
       <c r="C111" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>5</v>
@@ -1974,10 +1974,10 @@
         <v>1</v>
       </c>
       <c r="B112" s="2">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="C112" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>5</v>
@@ -1991,10 +1991,10 @@
         <v>46028</v>
       </c>
       <c r="C113" s="2">
-        <v>1411</v>
+        <v>5</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2002,10 +2002,10 @@
         <v>1</v>
       </c>
       <c r="B114" s="2">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="C114" s="2">
-        <v>460</v>
+        <v>6</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>5</v>
@@ -2019,7 +2019,7 @@
         <v>46030</v>
       </c>
       <c r="C115" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>5</v>
@@ -2033,7 +2033,7 @@
         <v>46031</v>
       </c>
       <c r="C116" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>5</v>
@@ -2047,10 +2047,10 @@
         <v>46031</v>
       </c>
       <c r="C117" s="2">
-        <v>2</v>
+        <v>145</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2058,13 +2058,13 @@
         <v>1</v>
       </c>
       <c r="B118" s="2">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="C118" s="2">
-        <v>837</v>
+        <v>105</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2072,10 +2072,10 @@
         <v>1</v>
       </c>
       <c r="B119" s="2">
-        <v>46031</v>
+        <v>46033</v>
       </c>
       <c r="C119" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>5</v>
@@ -2086,10 +2086,10 @@
         <v>1</v>
       </c>
       <c r="B120" s="2">
-        <v>46031</v>
+        <v>46033</v>
       </c>
       <c r="C120" s="2">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>5</v>
@@ -2100,10 +2100,10 @@
         <v>1</v>
       </c>
       <c r="B121" s="2">
-        <v>46032</v>
+        <v>46033</v>
       </c>
       <c r="C121" s="2">
-        <v>2029</v>
+        <v>7</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>5</v>
@@ -2114,13 +2114,13 @@
         <v>1</v>
       </c>
       <c r="B122" s="2">
-        <v>46023</v>
+        <v>46033</v>
       </c>
       <c r="C122" s="2">
-        <v>528</v>
+        <v>2</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2131,7 +2131,7 @@
         <v>46023</v>
       </c>
       <c r="C123" s="2">
-        <v>936</v>
+        <v>56</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>5</v>
@@ -2145,7 +2145,7 @@
         <v>46024</v>
       </c>
       <c r="C124" s="2">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>5</v>
@@ -2170,10 +2170,10 @@
         <v>1</v>
       </c>
       <c r="B126" s="2">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C126" s="2">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>5</v>
@@ -2184,13 +2184,13 @@
         <v>1</v>
       </c>
       <c r="B127" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C127" s="2">
-        <v>311</v>
+        <v>89</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2198,13 +2198,13 @@
         <v>1</v>
       </c>
       <c r="B128" s="2">
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="C128" s="2">
-        <v>969</v>
+        <v>406</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2212,13 +2212,13 @@
         <v>1</v>
       </c>
       <c r="B129" s="2">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="C129" s="2">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2226,10 +2226,10 @@
         <v>1</v>
       </c>
       <c r="B130" s="2">
-        <v>46028</v>
+        <v>46025</v>
       </c>
       <c r="C130" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>5</v>
@@ -2240,13 +2240,13 @@
         <v>1</v>
       </c>
       <c r="B131" s="2">
-        <v>46029</v>
+        <v>46026</v>
       </c>
       <c r="C131" s="2">
-        <v>183</v>
+        <v>81</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2254,13 +2254,13 @@
         <v>1</v>
       </c>
       <c r="B132" s="2">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="C132" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2268,13 +2268,13 @@
         <v>1</v>
       </c>
       <c r="B133" s="2">
-        <v>46030</v>
+        <v>46028</v>
       </c>
       <c r="C133" s="2">
-        <v>100</v>
+        <v>258</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2282,10 +2282,10 @@
         <v>1</v>
       </c>
       <c r="B134" s="2">
-        <v>46032</v>
+        <v>46029</v>
       </c>
       <c r="C134" s="2">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>5</v>
@@ -2296,13 +2296,13 @@
         <v>1</v>
       </c>
       <c r="B135" s="2">
-        <v>46032</v>
+        <v>46031</v>
       </c>
       <c r="C135" s="2">
-        <v>130</v>
+        <v>7</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2310,13 +2310,13 @@
         <v>1</v>
       </c>
       <c r="B136" s="2">
-        <v>46032</v>
+        <v>46031</v>
       </c>
       <c r="C136" s="2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2324,13 +2324,13 @@
         <v>1</v>
       </c>
       <c r="B137" s="2">
-        <v>46033</v>
+        <v>46032</v>
       </c>
       <c r="C137" s="2">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
